--- a/Data/EXCEL/Transfer/salemon/202412/8420-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/8420-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CDABEDB-78A0-471F-AB86-1FE07B86680D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48DBC649-AC68-4BB2-9019-A7DBAFF0845D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{B12D9E1F-244C-47E2-8306-B4425407D222}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{04EE7A8C-9167-4239-A002-28835C77A217}"/>
   </bookViews>
   <sheets>
     <sheet name="8420-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1255,21 +1255,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD8C8F88-E109-4459-8E58-1A5FAA4A065A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C95B453-76B5-47A2-A6A2-82956AD4A18A}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" customWidth="1"/>
-    <col min="2" max="5" width="14.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" customWidth="1"/>
-    <col min="8" max="11" width="14.453125" customWidth="1"/>
-    <col min="12" max="12" width="13.7265625" customWidth="1"/>
-    <col min="13" max="16" width="14.453125" customWidth="1"/>
-    <col min="17" max="17" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="11" width="9.875" customWidth="1"/>
+    <col min="12" max="12" width="9.5" customWidth="1"/>
+    <col min="13" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1296,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1378,7 +1378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1417,7 +1417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45566</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>-70.400000000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45536</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>-74.8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45505</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>-76.7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>45474</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>-79.3</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45444</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>-83.1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45413</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>-85.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45383</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>-89.2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>45352</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>-92.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45323</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>-96.4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>45292</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>-96</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45261</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>45231</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45200</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>-3.55</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>45170</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>45139</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>45108</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>45078</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>45047</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>45017</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>44986</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>37.700000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>44958</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>42.3</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>44927</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>44896</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>44866</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>44835</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>44805</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>44774</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>44743</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>44713</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>44682</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>44652</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>44621</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>44593</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>44562</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>44531</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>44501</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>68.599999999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>44470</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>44440</v>
       </c>
